--- a/giro_da_praça_ofertas - SABADO E DOMINGO.xlsx
+++ b/giro_da_praça_ofertas - SABADO E DOMINGO.xlsx
@@ -476,14 +476,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="54" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -546,7 +546,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SABADO/DOMINGO - PERECIVEIS 17 E 18/01/26</t>
+          <t>SEXTA/DOMINGO - PERECIVEIS 16 A 18/01/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -555,73 +555,77 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>101874</v>
+        <v>322738</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>TODDYNHO 200ML CHOCOLATE</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr"/>
+          <t>IOGURTE ACTIVIA 800G</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>AVEIA, MORANGO</t>
+        </is>
+      </c>
       <c r="F3" s="6" t="n">
-        <v>2.89</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SEXTA/DOMINGO - PERECIVEIS 16 A 18/01/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - LATICÍNIOS - BEBIDAS LACTEAS</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>322739</v>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>IOGURTE LIQUIDO ACTIVIA 800G AMEIXA</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="6" t="n">
+        <v>17.99</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SABADO/DOMINGO - BIRITA 17 E 18/01/2026</t>
+          <t>SABADO/DOMINGO - PERECIVEIS 17 E 18/01/26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
+          <t>#02 MERCEARIA - LATICÍNIOS - BEBIDAS LACTEAS</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>302070</v>
+        <v>101874</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>BEBIDA MISTA BEATS 269ML GIN E FRUTAS TROPICAIS</t>
+          <t>TODDYNHO 200ML CHOCOLATE</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr"/>
       <c r="F5" s="6" t="n">
-        <v>8.789999999999999</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - BIRITA 17 E 18/01/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - #00 ENERGÉTICOS</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>117100</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>ENERGETICO EXTRA POWER 2L</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="6" t="n">
-        <v>13.99</v>
-      </c>
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -631,20 +635,20 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJAS</t>
+          <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>259118</v>
+        <v>302070</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>CERVEJA SPATEN PURO MALTE LONG NECK 355ML</t>
+          <t>BEBIDA MISTA BEATS 269ML GIN E FRUTAS TROPICAIS</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr"/>
       <c r="F7" s="6" t="n">
-        <v>5.99</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -655,20 +659,20 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJAS CX</t>
+          <t>#05 BEBIDA - #00 ENERGÉTICOS</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>287369</v>
+        <v>117100</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERVEJA ANTARCTICA ORIGINAL 15 X 269ML </t>
+          <t>ENERGETICO EXTRA POWER 2L</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr"/>
       <c r="F8" s="6" t="n">
-        <v>3.89</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="9">
@@ -679,20 +683,20 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJAS CX</t>
+          <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>313599</v>
+        <v>259118</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>CERVEJA BUDWEISER 15 X 269ML</t>
+          <t>CERVEJA SPATEN PURO MALTE LONG NECK 355ML</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr"/>
       <c r="F9" s="6" t="n">
-        <v>3.59</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="10">
@@ -703,20 +707,20 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>236673</v>
+        <v>287369</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>BEBIDA ALCOOLICA FIU FIU 750ML TANGERINA ACEROLA</t>
+          <t xml:space="preserve">CERVEJA ANTARCTICA ORIGINAL 15 X 269ML </t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr"/>
       <c r="F10" s="6" t="n">
-        <v>41.99</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="11">
@@ -727,20 +731,20 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>293188</v>
+        <v>313599</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>CACHAÇA 51 600ML RAIZ</t>
+          <t>CERVEJA BUDWEISER 15 X 269ML</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr"/>
       <c r="F11" s="6" t="n">
-        <v>6.99</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="12">
@@ -755,16 +759,16 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>215568</v>
+        <v>236673</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>CACHAÇA BANANAZINHA 900ML</t>
+          <t>BEBIDA ALCOOLICA FIU FIU 750ML TANGERINA ACEROLA</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr"/>
       <c r="F12" s="6" t="n">
-        <v>36.99</v>
+        <v>41.99</v>
       </c>
     </row>
     <row r="13">
@@ -779,16 +783,16 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>191082</v>
+        <v>293188</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACHAÇA YPIOCA 965ML OURO SEM PALHA </t>
+          <t>CACHAÇA 51 600ML RAIZ</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr"/>
       <c r="F13" s="6" t="n">
-        <v>30.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="14">
@@ -803,16 +807,16 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>301843</v>
+        <v>215568</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>CAMPARI 998ML</t>
+          <t>CACHAÇA BANANAZINHA 900ML</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr"/>
       <c r="F14" s="6" t="n">
-        <v>78.98999999999999</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="15">
@@ -827,16 +831,16 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>265834</v>
+        <v>191082</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>CONHAQUE DOMUS 900ML GENGIBRE</t>
+          <t xml:space="preserve">CACHAÇA YPIOCA 965ML OURO SEM PALHA </t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr"/>
       <c r="F15" s="6" t="n">
-        <v>16.99</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="16">
@@ -851,16 +855,16 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>336250</v>
+        <v>301843</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">COQUETEL RAIZES AMARGAS 880ML DA RAÇA </t>
+          <t>CAMPARI 998ML</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr"/>
       <c r="F16" s="6" t="n">
-        <v>11.99</v>
+        <v>78.98999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -875,16 +879,16 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>206930</v>
+        <v>265834</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>GIN TANQUERAY 750ML LONDON</t>
+          <t>CONHAQUE DOMUS 900ML GENGIBRE</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr"/>
       <c r="F17" s="6" t="n">
-        <v>144</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="18">
@@ -899,16 +903,16 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>102212</v>
+        <v>336250</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>RUM MONTILLA 1L CARTA BRANCA</t>
+          <t xml:space="preserve">COQUETEL RAIZES AMARGAS 880ML DA RAÇA </t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr"/>
       <c r="F18" s="6" t="n">
-        <v>34.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="19">
@@ -923,16 +927,16 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>102093</v>
+        <v>206930</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>VODKA ORLOFF 1L CRISTAL</t>
+          <t>GIN TANQUERAY 750ML LONDON</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr"/>
       <c r="F19" s="6" t="n">
-        <v>42.99</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20">
@@ -947,16 +951,16 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>110367</v>
+        <v>102212</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>WHISKY JACK DANIELS 1L</t>
+          <t>RUM MONTILLA 1L CARTA BRANCA</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr"/>
       <c r="F20" s="6" t="n">
-        <v>197.1</v>
+        <v>34.99</v>
       </c>
     </row>
     <row r="21">
@@ -971,16 +975,16 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>102082</v>
+        <v>102093</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>WHISKY PASSPORT 1L</t>
+          <t>VODKA ORLOFF 1L CRISTAL</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr"/>
       <c r="F21" s="6" t="n">
-        <v>73.98999999999999</v>
+        <v>42.99</v>
       </c>
     </row>
     <row r="22">
@@ -995,16 +999,16 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>109729</v>
+        <v>110367</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>WHISKY WHITE HORSE 1L</t>
+          <t>WHISKY JACK DANIELS 1L</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr"/>
       <c r="F22" s="6" t="n">
-        <v>99.98999999999999</v>
+        <v>197.1</v>
       </c>
     </row>
     <row r="23">
@@ -1015,77 +1019,77 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - FERMENTADOS</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>102036</v>
+        <v>102082</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>VINHO GALIOTTO 1L TINTO SUAVE</t>
+          <t>WHISKY PASSPORT 1L</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr"/>
       <c r="F23" s="6" t="n">
-        <v>24.99</v>
+        <v>73.98999999999999</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SABADO/DOMINGO - BIRITA 17 E 18/01/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - DESTILADOS</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>109729</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>WHISKY WHITE HORSE 1L</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="6" t="n">
+        <v>99.98999999999999</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>SABADO/DOMINGO - PERECIVEIS 17 E 18/01/26</t>
+          <t>SABADO/DOMINGO - BIRITA 17 E 18/01/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #01 AVES</t>
+          <t>#05 BEBIDA - FERMENTADOS</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>104602</v>
+        <v>102036</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>COXA DE FRANGO SADIA PCT 1KG</t>
+          <t>VINHO GALIOTTO 1L TINTO SUAVE</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr"/>
       <c r="F25" s="6" t="n">
-        <v>13.99</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>SABADO/DOMINGO - PERECIVEIS 17 E 18/01/26</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #01 AVES</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>147352</v>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>COXINHA DA ASA DE FRANGO SADIA BDJ 1KG</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="6" t="n">
-        <v>20.99</v>
-      </c>
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1099,16 +1103,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>108783</v>
+        <v>104602</v>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>MEIO DA ASA DE FRANGO SADIA BDJ 1KG</t>
+          <t>COXA DE FRANGO SADIA PCT 1KG</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr"/>
       <c r="F27" s="6" t="n">
-        <v>25.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="28">
@@ -1123,16 +1127,16 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>108773</v>
+        <v>147352</v>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>MOELA DE FRANGO SADIA BDJ 1KG</t>
+          <t>COXINHA DA ASA DE FRANGO SADIA BDJ 1KG</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr"/>
       <c r="F28" s="6" t="n">
-        <v>18.49</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="29">
@@ -1147,16 +1151,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>104601</v>
+        <v>108783</v>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>SOBRECOXA DE FRANGO SADIA PCT 1KG</t>
+          <t>MEIO DA ASA DE FRANGO SADIA BDJ 1KG</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr"/>
       <c r="F29" s="6" t="n">
-        <v>16.99</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="30">
@@ -1167,20 +1171,20 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+          <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>194424</v>
+        <v>108773</v>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>LINGUIÇA CALABRESA BOUA 400G</t>
+          <t>MOELA DE FRANGO SADIA BDJ 1KG</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="6" t="n">
-        <v>13.99</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="31">
@@ -1191,92 +1195,428 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+          <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>289127</v>
+        <v>104601</v>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>LINGUIÇA MISTA FININHA DEFUMADA SADIA 215G</t>
+          <t>SOBRECOXA DE FRANGO SADIA PCT 1KG</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="6" t="n">
-        <v>7.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>SABADO/DOMINGO - PERECIVEIS 17 E 18/01/26</t>
+          <t>SEXTA/DOMINGO - PERECIVEIS 16 A 18/01/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+          <t>#06 AÇOUGUE - #04 PEIXES</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>272499</v>
+        <v>311307</v>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>LINGUIÇA SUINA FARIAS KG</t>
+          <t>BOLINHO DE TILAPIA 270G CONGELADO</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr"/>
       <c r="F32" s="6" t="n">
-        <v>22.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>SABADO/DOMINGO - PERECIVEIS 17 E 18/01/26</t>
+          <t>SEXTA/DOMINGO - PERECIVEIS 16 A 18/01/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+          <t>#06 AÇOUGUE - #04 PEIXES</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>167154</v>
+        <v>164660</v>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>LINGUIÇA SUINA FINA APIMENTADA FRICÓ KG</t>
+          <t>CAÇÃO EM POSTAS COSTA SUL 800G CONGELADO</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr"/>
       <c r="F33" s="6" t="n">
-        <v>24.99</v>
+        <v>35.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>SABADO/DOMINGO - PERECIVEIS 17 E 18/01/26</t>
+          <t>SEXTA/DOMINGO - PERECIVEIS 16 A 18/01/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+          <t>#06 AÇOUGUE - #04 PEIXES</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>120546</v>
+        <v>284245</v>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>SALAME ITALIANO SADIA 100G FATIADO</t>
+          <t>PEIXITOS COSTA SUL 300G</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr"/>
       <c r="F34" s="6" t="n">
+        <v>10.39</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>SEXTA/DOMINGO - PERECIVEIS 16 A 18/01/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #04 PEIXES</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>255039</v>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>QUADRITOS DE PEIXE COSTA SUL 400G</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="6" t="n">
         <v>14.99</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>SEXTA/DOMINGO - PERECIVEIS 16 A 18/01/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #04 PEIXES</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>195294</v>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SARDINHAS INTEIRAS COSTA SUL CONGELADAS 800G 06/15 </t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="6" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>SEXTA/DOMINGO - PERECIVEIS 16 A 18/01/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #05 FRUTOS DO MAR</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>323487</v>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>CAMARAO COSTA SUL 300G VAN SEM CABEÇA COZIDO</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr"/>
+      <c r="F37" s="6" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>SEXTA/DOMINGO - PERECIVEIS 16 A 18/01/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #05 FRUTOS DO MAR</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>323495</v>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>CAMARÃO COSTA SUL 300G COZIDO DECASCADO</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr"/>
+      <c r="F38" s="6" t="n">
+        <v>43.99</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>SEXTA/DOMINGO - PERECIVEIS 16 A 18/01/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #05 FRUTOS DO MAR</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>325492</v>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>KIT PAELLA COSTA SUL 300GR CAMARÃO E LULA</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr"/>
+      <c r="F39" s="6" t="n">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>SEXTA/DOMINGO - PERECIVEIS 16 A 18/01/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #05 FRUTOS DO MAR</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>323489</v>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>MEXILHÃO COSTA SUL 300G MARISCO DESCONCHADO</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr"/>
+      <c r="F40" s="6" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>SABADO/DOMINGO - PERECIVEIS 17 E 18/01/26</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>194424</v>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>LINGUIÇA CALABRESA BOUA 400G</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr"/>
+      <c r="F41" s="6" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>SABADO/DOMINGO - PERECIVEIS 17 E 18/01/26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>289127</v>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>LINGUIÇA MISTA FININHA DEFUMADA SADIA 215G</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr"/>
+      <c r="F42" s="6" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>SABADO/DOMINGO - PERECIVEIS 17 E 18/01/26</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>272499</v>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>LINGUIÇA SUINA FARIAS KG</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr"/>
+      <c r="F43" s="6" t="n">
+        <v>22.99</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>SABADO/DOMINGO - PERECIVEIS 17 E 18/01/26</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>167154</v>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>LINGUIÇA SUINA FINA APIMENTADA FRICÓ KG</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr"/>
+      <c r="F44" s="6" t="n">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>SABADO/DOMINGO - PERECIVEIS 17 E 18/01/26</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>120546</v>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>SALAME ITALIANO SADIA 100G FATIADO</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr"/>
+      <c r="F45" s="6" t="n">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>SEXTA/DOMINGO - PERECIVEIS 16 A 18/01/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>120962</v>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>BOLINHO DE BACALHAU COSTA SUL CONGELADO 270G</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr"/>
+      <c r="F46" s="6" t="n">
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>SEXTA/DOMINGO - PERECIVEIS 16 A 18/01/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>260606</v>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>STEAK EMPANADO COSTA SUL 100G PEIXE</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr"/>
+      <c r="F47" s="6" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>SEXTA/DOMINGO - PERECIVEIS 16 A 18/01/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>284246</v>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>TIRINHAS DE TILÁPIA COSTA SUL 300G EMPANADO</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr"/>
+      <c r="F48" s="6" t="n">
+        <v>11.49</v>
       </c>
     </row>
   </sheetData>

--- a/giro_da_praça_ofertas - SABADO E DOMINGO.xlsx
+++ b/giro_da_praça_ofertas - SABADO E DOMINGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A43427-70B6-46F2-B888-F1A8C5AFB61E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0535E2FB-A0FF-4608-81A1-782869386448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -281,7 +281,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -318,25 +318,32 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <sz val="7"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -347,24 +354,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45A045"/>
-        <bgColor rgb="FF45A045"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FF45A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -395,7 +384,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -412,40 +401,30 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -759,7 +738,7 @@
     <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="47.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -778,423 +757,423 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="10">
         <v>102282</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="14"/>
-      <c r="F2" s="15">
+      <c r="E2" s="12"/>
+      <c r="F2" s="13">
         <v>8.99</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="10">
         <v>171895</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="14"/>
-      <c r="F3" s="15">
+      <c r="E3" s="12"/>
+      <c r="F3" s="13">
         <v>4.8899999999999997</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="A4" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="10">
         <v>259118</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="14"/>
-      <c r="F4" s="15">
+      <c r="E4" s="12"/>
+      <c r="F4" s="13">
         <v>5.99</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="6" t="s">
+      <c r="A5" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="10">
         <v>168712</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="16"/>
-      <c r="F5" s="17">
+      <c r="E5" s="11"/>
+      <c r="F5" s="13">
         <f>15*3.19</f>
         <v>47.85</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="6" t="s">
+      <c r="A6" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="10">
         <v>265727</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="17">
+      <c r="E6" s="11"/>
+      <c r="F6" s="13">
         <f>8*4.69</f>
         <v>37.520000000000003</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="A7" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="10">
         <v>108084</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="14"/>
-      <c r="F7" s="15">
+      <c r="E7" s="12"/>
+      <c r="F7" s="13">
         <v>8.5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="A8" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="10">
         <v>193636</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="14"/>
-      <c r="F8" s="15">
+      <c r="E8" s="12"/>
+      <c r="F8" s="13">
         <v>11.19</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="A9" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="10">
         <v>220282</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="14"/>
-      <c r="F9" s="15">
+      <c r="E9" s="12"/>
+      <c r="F9" s="13">
         <v>40.99</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="A10" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="10">
         <v>236673</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="14"/>
-      <c r="F10" s="15">
+      <c r="E10" s="12"/>
+      <c r="F10" s="13">
         <v>42.99</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="10">
         <v>102085</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="14"/>
-      <c r="F11" s="15">
+      <c r="E11" s="12"/>
+      <c r="F11" s="13">
         <v>12.99</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="A12" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="10">
         <v>215568</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="14"/>
-      <c r="F12" s="15">
+      <c r="E12" s="12"/>
+      <c r="F12" s="13">
         <v>38.99</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="A13" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="10">
         <v>210317</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="14"/>
-      <c r="F13" s="15">
+      <c r="E13" s="12"/>
+      <c r="F13" s="13">
         <v>54.99</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="2" t="s">
+      <c r="A14" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="10">
         <v>301843</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="14"/>
-      <c r="F14" s="15">
+      <c r="E14" s="12"/>
+      <c r="F14" s="13">
         <v>77.989999999999995</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="A15" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="10">
         <v>265834</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="14"/>
-      <c r="F15" s="15">
+      <c r="E15" s="12"/>
+      <c r="F15" s="13">
         <v>16.989999999999998</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="A16" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="10">
         <v>284865</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="14"/>
-      <c r="F16" s="15">
+      <c r="E16" s="12"/>
+      <c r="F16" s="13">
         <v>33.99</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" s="2" t="s">
+      <c r="A17" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="10">
         <v>230698</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="14"/>
-      <c r="F17" s="15">
+      <c r="E17" s="12"/>
+      <c r="F17" s="13">
         <v>254.99</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="2" t="s">
+      <c r="A18" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="10">
         <v>145658</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="14"/>
-      <c r="F18" s="15">
+      <c r="E18" s="12"/>
+      <c r="F18" s="13">
         <v>105.99</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" s="2" t="s">
+      <c r="A19" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="10">
         <v>102087</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="14"/>
-      <c r="F19" s="15">
+      <c r="E19" s="12"/>
+      <c r="F19" s="13">
         <v>49.99</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="2" t="s">
+      <c r="A20" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="10">
         <v>334785</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="14"/>
-      <c r="F20" s="15">
+      <c r="E20" s="12"/>
+      <c r="F20" s="13">
         <v>138.99</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="A21" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="10">
         <v>109727</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E21" s="14"/>
-      <c r="F21" s="15">
+      <c r="E21" s="12"/>
+      <c r="F21" s="13">
         <v>179.99</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="2" t="s">
+      <c r="A22" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="10">
         <v>102077</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E22" s="14"/>
-      <c r="F22" s="15">
+      <c r="E22" s="12"/>
+      <c r="F22" s="13">
         <v>179.99</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="2" t="s">
+      <c r="A23" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="10">
         <v>206457</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E23" s="14"/>
-      <c r="F23" s="15">
+      <c r="E23" s="12"/>
+      <c r="F23" s="13">
         <v>56.99</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" s="2" t="s">
+      <c r="A24" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="10">
         <v>102036</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D24" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="14"/>
-      <c r="F24" s="15">
+      <c r="E24" s="12"/>
+      <c r="F24" s="13">
         <v>23.99</v>
       </c>
     </row>
@@ -1212,7 +1191,7 @@
         <v>37</v>
       </c>
       <c r="E26" s="5"/>
-      <c r="F26" s="10">
+      <c r="F26" s="7">
         <v>8.99</v>
       </c>
     </row>
@@ -1230,7 +1209,7 @@
         <v>38</v>
       </c>
       <c r="E27" s="5"/>
-      <c r="F27" s="10">
+      <c r="F27" s="7">
         <v>6.59</v>
       </c>
     </row>
@@ -1248,7 +1227,7 @@
         <v>39</v>
       </c>
       <c r="E28" s="5"/>
-      <c r="F28" s="10">
+      <c r="F28" s="7">
         <v>6.89</v>
       </c>
     </row>
@@ -1266,7 +1245,7 @@
         <v>40</v>
       </c>
       <c r="E29" s="5"/>
-      <c r="F29" s="10">
+      <c r="F29" s="7">
         <v>4.59</v>
       </c>
     </row>
@@ -1284,7 +1263,7 @@
         <v>41</v>
       </c>
       <c r="E30" s="5"/>
-      <c r="F30" s="10">
+      <c r="F30" s="7">
         <v>6.99</v>
       </c>
     </row>
@@ -1302,7 +1281,7 @@
         <v>42</v>
       </c>
       <c r="E31" s="5"/>
-      <c r="F31" s="10">
+      <c r="F31" s="7">
         <v>6.99</v>
       </c>
     </row>
@@ -1320,7 +1299,7 @@
         <v>43</v>
       </c>
       <c r="E32" s="5"/>
-      <c r="F32" s="10">
+      <c r="F32" s="7">
         <v>12.99</v>
       </c>
     </row>
@@ -1338,7 +1317,7 @@
         <v>44</v>
       </c>
       <c r="E33" s="5"/>
-      <c r="F33" s="10">
+      <c r="F33" s="7">
         <v>15.99</v>
       </c>
     </row>
@@ -1356,7 +1335,7 @@
         <v>45</v>
       </c>
       <c r="E34" s="5"/>
-      <c r="F34" s="10">
+      <c r="F34" s="7">
         <v>6.99</v>
       </c>
     </row>
@@ -1374,7 +1353,7 @@
         <v>46</v>
       </c>
       <c r="E35" s="5"/>
-      <c r="F35" s="10">
+      <c r="F35" s="7">
         <v>14.99</v>
       </c>
     </row>
@@ -1392,7 +1371,7 @@
         <v>48</v>
       </c>
       <c r="E36" s="5"/>
-      <c r="F36" s="10">
+      <c r="F36" s="7">
         <v>5.39</v>
       </c>
     </row>
@@ -1410,7 +1389,7 @@
         <v>49</v>
       </c>
       <c r="E37" s="5"/>
-      <c r="F37" s="10">
+      <c r="F37" s="7">
         <v>7.49</v>
       </c>
     </row>
@@ -1428,7 +1407,7 @@
         <v>50</v>
       </c>
       <c r="E38" s="5"/>
-      <c r="F38" s="10">
+      <c r="F38" s="7">
         <v>5.19</v>
       </c>
     </row>
@@ -1446,7 +1425,7 @@
         <v>51</v>
       </c>
       <c r="E39" s="5"/>
-      <c r="F39" s="10">
+      <c r="F39" s="7">
         <v>7.19</v>
       </c>
     </row>
@@ -1464,7 +1443,7 @@
         <v>53</v>
       </c>
       <c r="E40" s="5"/>
-      <c r="F40" s="10">
+      <c r="F40" s="7">
         <v>3.79</v>
       </c>
     </row>
@@ -1482,332 +1461,348 @@
         <v>55</v>
       </c>
       <c r="E42" s="5"/>
-      <c r="F42" s="10">
+      <c r="F42" s="7">
         <f>12*0.59</f>
         <v>7.08</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C44" s="7">
+      <c r="C44" s="10">
         <v>311307</v>
       </c>
-      <c r="D44" s="8" t="s">
+      <c r="D44" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="E44" s="8"/>
-      <c r="F44" s="11">
+      <c r="E44" s="11"/>
+      <c r="F44" s="13">
         <v>16.989999999999998</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C45" s="7">
+      <c r="C45" s="10">
         <v>164658</v>
       </c>
-      <c r="D45" s="8" t="s">
+      <c r="D45" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="E45" s="8"/>
-      <c r="F45" s="11">
+      <c r="E45" s="11"/>
+      <c r="F45" s="13">
         <v>35.99</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C46" s="7">
+      <c r="C46" s="10">
         <v>323499</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="D46" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="E46" s="8"/>
-      <c r="F46" s="11">
+      <c r="E46" s="11"/>
+      <c r="F46" s="13">
         <v>64.989999999999995</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C47" s="7">
+      <c r="C47" s="10">
         <v>323489</v>
       </c>
-      <c r="D47" s="8" t="s">
+      <c r="D47" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="E47" s="8"/>
-      <c r="F47" s="11">
+      <c r="E47" s="11"/>
+      <c r="F47" s="13">
         <v>25.99</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C48" s="7">
+      <c r="C48" s="10">
         <v>189031</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="D48" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E48" s="8"/>
-      <c r="F48" s="11">
+      <c r="E48" s="11"/>
+      <c r="F48" s="13">
         <v>18.989999999999998</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C49" s="7">
+      <c r="C49" s="10">
         <v>284246</v>
       </c>
-      <c r="D49" s="8" t="s">
+      <c r="D49" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="E49" s="8"/>
-      <c r="F49" s="11">
+      <c r="E49" s="11"/>
+      <c r="F49" s="13">
         <v>11.99</v>
       </c>
     </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="14"/>
+      <c r="B50" s="14"/>
+      <c r="C50" s="14"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="14"/>
+      <c r="F50" s="15"/>
+    </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C51" s="7">
+      <c r="C51" s="10">
         <v>336608</v>
       </c>
-      <c r="D51" s="8" t="s">
+      <c r="D51" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="E51" s="8"/>
-      <c r="F51" s="11">
+      <c r="E51" s="11"/>
+      <c r="F51" s="13">
         <v>11.99</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C52" s="7">
+      <c r="C52" s="10">
         <v>276943</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="D52" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E52" s="8"/>
-      <c r="F52" s="11">
+      <c r="E52" s="11"/>
+      <c r="F52" s="13">
         <v>15.99</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C53" s="7">
+      <c r="C53" s="10">
         <v>270325</v>
       </c>
-      <c r="D53" s="8" t="s">
+      <c r="D53" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="E53" s="8"/>
-      <c r="F53" s="11">
+      <c r="E53" s="11"/>
+      <c r="F53" s="13">
         <v>10.99</v>
       </c>
     </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="14"/>
+      <c r="B54" s="14"/>
+      <c r="C54" s="14"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="15"/>
+    </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C55" s="7">
+      <c r="C55" s="10">
         <v>289789</v>
       </c>
-      <c r="D55" s="8" t="s">
+      <c r="D55" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="E55" s="8"/>
-      <c r="F55" s="11">
+      <c r="E55" s="11"/>
+      <c r="F55" s="13">
         <v>12.99</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C56" s="7">
+      <c r="C56" s="10">
         <v>289786</v>
       </c>
-      <c r="D56" s="8" t="s">
+      <c r="D56" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="E56" s="8"/>
-      <c r="F56" s="11">
+      <c r="E56" s="11"/>
+      <c r="F56" s="13">
         <v>16.989999999999998</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C57" s="7">
+      <c r="C57" s="10">
         <v>289796</v>
       </c>
-      <c r="D57" s="8" t="s">
+      <c r="D57" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="E57" s="8"/>
-      <c r="F57" s="11">
+      <c r="E57" s="11"/>
+      <c r="F57" s="13">
         <v>19.989999999999998</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C58" s="7">
+      <c r="C58" s="10">
         <v>289795</v>
       </c>
-      <c r="D58" s="8" t="s">
+      <c r="D58" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="E58" s="8"/>
-      <c r="F58" s="11">
+      <c r="E58" s="11"/>
+      <c r="F58" s="13">
         <v>13.99</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C59" s="7">
+      <c r="C59" s="10">
         <v>298984</v>
       </c>
-      <c r="D59" s="8" t="s">
+      <c r="D59" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="E59" s="8"/>
-      <c r="F59" s="11">
+      <c r="E59" s="11"/>
+      <c r="F59" s="13">
         <v>13.99</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C60" s="7">
+      <c r="C60" s="10">
         <v>320121</v>
       </c>
-      <c r="D60" s="8" t="s">
+      <c r="D60" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="E60" s="8"/>
-      <c r="F60" s="11">
+      <c r="E60" s="11"/>
+      <c r="F60" s="13">
         <v>23.99</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C61" s="7">
+      <c r="C61" s="10">
         <v>302029</v>
       </c>
-      <c r="D61" s="8" t="s">
+      <c r="D61" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="E61" s="8"/>
-      <c r="F61" s="11">
+      <c r="E61" s="11"/>
+      <c r="F61" s="13">
         <v>22.99</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="6" t="s">
+      <c r="A62" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C62" s="7">
+      <c r="C62" s="10">
         <v>272499</v>
       </c>
-      <c r="D62" s="8" t="s">
+      <c r="D62" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="E62" s="8"/>
-      <c r="F62" s="11">
+      <c r="E62" s="11"/>
+      <c r="F62" s="13">
         <v>23.49</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C63" s="7">
+      <c r="C63" s="10">
         <v>292399</v>
       </c>
-      <c r="D63" s="8" t="s">
+      <c r="D63" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="E63" s="8"/>
-      <c r="F63" s="11">
+      <c r="E63" s="11"/>
+      <c r="F63" s="13">
         <v>10.99</v>
       </c>
     </row>

--- a/giro_da_praça_ofertas - SABADO E DOMINGO.xlsx
+++ b/giro_da_praça_ofertas - SABADO E DOMINGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0535E2FB-A0FF-4608-81A1-782869386448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37A5ADE-983A-4703-93F2-6E023C29834C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -281,7 +281,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -301,46 +301,65 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
+      <sz val="7"/>
+      <color theme="1"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="7"/>
+      <b/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -384,7 +403,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -392,39 +411,44 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -731,1083 +755,1086 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F63"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="33" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="36" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.28515625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5703125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="81.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="9" t="s">
+    <row r="2" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="7">
         <v>102282</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="13">
+      <c r="E2" s="9"/>
+      <c r="F2" s="16">
         <v>8.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="9" t="s">
+    <row r="3" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="7">
         <v>171895</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="12"/>
-      <c r="F3" s="13">
+      <c r="E3" s="9"/>
+      <c r="F3" s="16">
         <v>4.8899999999999997</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="9" t="s">
+    <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="7">
         <v>259118</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="13">
+      <c r="E4" s="9"/>
+      <c r="F4" s="16">
         <v>5.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="9" t="s">
+    <row r="5" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="7">
         <v>168712</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="13">
+      <c r="E5" s="8"/>
+      <c r="F5" s="16">
         <f>15*3.19</f>
         <v>47.85</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="9" t="s">
+    <row r="6" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="7">
         <v>265727</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="13">
+      <c r="E6" s="8"/>
+      <c r="F6" s="16">
         <f>8*4.69</f>
         <v>37.520000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="9" t="s">
+    <row r="7" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="7">
         <v>108084</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="13">
+      <c r="E7" s="9"/>
+      <c r="F7" s="16">
         <v>8.5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="9" t="s">
+    <row r="8" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="7">
         <v>193636</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="13">
+      <c r="E8" s="9"/>
+      <c r="F8" s="16">
         <v>11.19</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="9" t="s">
+    <row r="9" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="7">
         <v>220282</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="13">
+      <c r="E9" s="9"/>
+      <c r="F9" s="16">
         <v>40.99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="9" t="s">
+    <row r="10" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="7">
         <v>236673</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="13">
+      <c r="E10" s="9"/>
+      <c r="F10" s="16">
         <v>42.99</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="9" t="s">
+    <row r="11" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="7">
         <v>102085</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="13">
+      <c r="E11" s="9"/>
+      <c r="F11" s="16">
         <v>12.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="9" t="s">
+    <row r="12" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="7">
         <v>215568</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="13">
+      <c r="E12" s="9"/>
+      <c r="F12" s="16">
         <v>38.99</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="9" t="s">
+    <row r="13" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="7">
         <v>210317</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="13">
+      <c r="E13" s="9"/>
+      <c r="F13" s="16">
         <v>54.99</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="9" t="s">
+    <row r="14" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="7">
         <v>301843</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="13">
+      <c r="E14" s="9"/>
+      <c r="F14" s="16">
         <v>77.989999999999995</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="9" t="s">
+    <row r="15" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="7">
         <v>265834</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="13">
+      <c r="E15" s="9"/>
+      <c r="F15" s="16">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="9" t="s">
+    <row r="16" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="7">
         <v>284865</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="13">
+      <c r="E16" s="9"/>
+      <c r="F16" s="16">
         <v>33.99</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" s="9" t="s">
+    <row r="17" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="7">
         <v>230698</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="12"/>
-      <c r="F17" s="13">
+      <c r="E17" s="9"/>
+      <c r="F17" s="16">
         <v>254.99</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="9" t="s">
+    <row r="18" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="7">
         <v>145658</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="13">
+      <c r="E18" s="9"/>
+      <c r="F18" s="16">
         <v>105.99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" s="9" t="s">
+    <row r="19" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="7">
         <v>102087</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="12"/>
-      <c r="F19" s="13">
+      <c r="E19" s="9"/>
+      <c r="F19" s="16">
         <v>49.99</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="9" t="s">
+    <row r="20" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="7">
         <v>334785</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="13">
+      <c r="E20" s="9"/>
+      <c r="F20" s="16">
         <v>138.99</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="9" t="s">
+    <row r="21" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="7">
         <v>109727</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E21" s="12"/>
-      <c r="F21" s="13">
+      <c r="E21" s="9"/>
+      <c r="F21" s="16">
         <v>179.99</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="9" t="s">
+    <row r="22" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="7">
         <v>102077</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E22" s="12"/>
-      <c r="F22" s="13">
+      <c r="E22" s="9"/>
+      <c r="F22" s="16">
         <v>179.99</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="9" t="s">
+    <row r="23" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="7">
         <v>206457</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E23" s="12"/>
-      <c r="F23" s="13">
+      <c r="E23" s="9"/>
+      <c r="F23" s="16">
         <v>56.99</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" s="9" t="s">
+    <row r="24" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="10">
+      <c r="C24" s="7">
         <v>102036</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="12"/>
-      <c r="F24" s="13">
+      <c r="E24" s="9"/>
+      <c r="F24" s="16">
         <v>23.99</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="11">
         <v>104864</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="7">
+      <c r="E26" s="13"/>
+      <c r="F26" s="14">
         <v>8.99</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="11">
         <v>105023</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="7">
+      <c r="E27" s="13"/>
+      <c r="F27" s="14">
         <v>6.59</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="11">
         <v>104931</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="7">
+      <c r="E28" s="13"/>
+      <c r="F28" s="14">
         <v>6.89</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="11">
         <v>104855</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="7">
+      <c r="E29" s="13"/>
+      <c r="F29" s="14">
         <v>4.59</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="11">
         <v>104928</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="7">
+      <c r="E30" s="13"/>
+      <c r="F30" s="14">
         <v>6.99</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="11">
         <v>104883</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="7">
+      <c r="E31" s="13"/>
+      <c r="F31" s="14">
         <v>6.99</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="11">
         <v>108982</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="7">
+      <c r="E32" s="13"/>
+      <c r="F32" s="14">
         <v>12.99</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="11">
         <v>104944</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="7">
+      <c r="E33" s="13"/>
+      <c r="F33" s="14">
         <v>15.99</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="11">
         <v>104996</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="7">
+      <c r="E34" s="13"/>
+      <c r="F34" s="14">
         <v>6.99</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="11">
         <v>113290</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="7">
+      <c r="E35" s="13"/>
+      <c r="F35" s="14">
         <v>14.99</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="11">
         <v>105010</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E36" s="5"/>
-      <c r="F36" s="7">
+      <c r="E36" s="13"/>
+      <c r="F36" s="14">
         <v>5.39</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="11">
         <v>105001</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E37" s="5"/>
-      <c r="F37" s="7">
+      <c r="E37" s="13"/>
+      <c r="F37" s="14">
         <v>7.49</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="11">
         <v>104862</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="E38" s="5"/>
-      <c r="F38" s="7">
+      <c r="E38" s="13"/>
+      <c r="F38" s="14">
         <v>5.19</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="11">
         <v>104961</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E39" s="5"/>
-      <c r="F39" s="7">
+      <c r="E39" s="13"/>
+      <c r="F39" s="14">
         <v>7.19</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="11">
         <v>104919</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E40" s="5"/>
-      <c r="F40" s="7">
+      <c r="E40" s="13"/>
+      <c r="F40" s="14">
         <v>3.79</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="11">
         <v>239922</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="E42" s="5"/>
-      <c r="F42" s="7">
+      <c r="E42" s="13"/>
+      <c r="F42" s="14">
         <f>12*0.59</f>
         <v>7.08</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="9" t="s">
+    <row r="44" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C44" s="10">
+      <c r="C44" s="7">
         <v>311307</v>
       </c>
-      <c r="D44" s="11" t="s">
+      <c r="D44" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E44" s="11"/>
-      <c r="F44" s="13">
+      <c r="E44" s="8"/>
+      <c r="F44" s="16">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="9" t="s">
+    <row r="45" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C45" s="10">
+      <c r="C45" s="7">
         <v>164658</v>
       </c>
-      <c r="D45" s="11" t="s">
+      <c r="D45" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E45" s="11"/>
-      <c r="F45" s="13">
+      <c r="E45" s="8"/>
+      <c r="F45" s="16">
         <v>35.99</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="9" t="s">
+    <row r="46" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C46" s="10">
+      <c r="C46" s="7">
         <v>323499</v>
       </c>
-      <c r="D46" s="11" t="s">
+      <c r="D46" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="E46" s="11"/>
-      <c r="F46" s="13">
+      <c r="E46" s="8"/>
+      <c r="F46" s="16">
         <v>64.989999999999995</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="9" t="s">
+    <row r="47" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C47" s="10">
+      <c r="C47" s="7">
         <v>323489</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D47" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E47" s="11"/>
-      <c r="F47" s="13">
+      <c r="E47" s="8"/>
+      <c r="F47" s="16">
         <v>25.99</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="9" t="s">
+    <row r="48" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C48" s="10">
+      <c r="C48" s="7">
         <v>189031</v>
       </c>
-      <c r="D48" s="11" t="s">
+      <c r="D48" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="E48" s="11"/>
-      <c r="F48" s="13">
+      <c r="E48" s="8"/>
+      <c r="F48" s="16">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="9" t="s">
+    <row r="49" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C49" s="10">
+      <c r="C49" s="7">
         <v>284246</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D49" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="E49" s="11"/>
-      <c r="F49" s="13">
+      <c r="E49" s="8"/>
+      <c r="F49" s="16">
         <v>11.99</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="14"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="15"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="9" t="s">
+    <row r="50" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="4"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="18"/>
+    </row>
+    <row r="51" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C51" s="10">
+      <c r="C51" s="7">
         <v>336608</v>
       </c>
-      <c r="D51" s="11" t="s">
+      <c r="D51" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="E51" s="11"/>
-      <c r="F51" s="13">
+      <c r="E51" s="8"/>
+      <c r="F51" s="16">
         <v>11.99</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="9" t="s">
+    <row r="52" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C52" s="10">
+      <c r="C52" s="7">
         <v>276943</v>
       </c>
-      <c r="D52" s="11" t="s">
+      <c r="D52" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E52" s="11"/>
-      <c r="F52" s="13">
+      <c r="E52" s="8"/>
+      <c r="F52" s="16">
         <v>15.99</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="9" t="s">
+    <row r="53" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C53" s="10">
+      <c r="C53" s="7">
         <v>270325</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="D53" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="E53" s="11"/>
-      <c r="F53" s="13">
+      <c r="E53" s="8"/>
+      <c r="F53" s="16">
         <v>10.99</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="14"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="15"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="9" t="s">
+    <row r="54" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="4"/>
+      <c r="B54" s="4"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="18"/>
+    </row>
+    <row r="55" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C55" s="10">
+      <c r="C55" s="7">
         <v>289789</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D55" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E55" s="11"/>
-      <c r="F55" s="13">
+      <c r="E55" s="8"/>
+      <c r="F55" s="16">
         <v>12.99</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="9" t="s">
+    <row r="56" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B56" s="9" t="s">
+      <c r="B56" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C56" s="10">
+      <c r="C56" s="7">
         <v>289786</v>
       </c>
-      <c r="D56" s="11" t="s">
+      <c r="D56" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="E56" s="11"/>
-      <c r="F56" s="13">
+      <c r="E56" s="8"/>
+      <c r="F56" s="16">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="9" t="s">
+    <row r="57" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C57" s="10">
+      <c r="C57" s="7">
         <v>289796</v>
       </c>
-      <c r="D57" s="11" t="s">
+      <c r="D57" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="E57" s="11"/>
-      <c r="F57" s="13">
+      <c r="E57" s="8"/>
+      <c r="F57" s="16">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="9" t="s">
+    <row r="58" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C58" s="10">
+      <c r="C58" s="7">
         <v>289795</v>
       </c>
-      <c r="D58" s="11" t="s">
+      <c r="D58" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E58" s="11"/>
-      <c r="F58" s="13">
+      <c r="E58" s="8"/>
+      <c r="F58" s="16">
         <v>13.99</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="9" t="s">
+    <row r="59" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C59" s="10">
+      <c r="C59" s="7">
         <v>298984</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="D59" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="E59" s="11"/>
-      <c r="F59" s="13">
+      <c r="E59" s="8"/>
+      <c r="F59" s="16">
         <v>13.99</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="9" t="s">
+    <row r="60" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C60" s="10">
+      <c r="C60" s="7">
         <v>320121</v>
       </c>
-      <c r="D60" s="11" t="s">
+      <c r="D60" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="E60" s="11"/>
-      <c r="F60" s="13">
+      <c r="E60" s="8"/>
+      <c r="F60" s="16">
         <v>23.99</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="9" t="s">
+    <row r="61" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C61" s="10">
+      <c r="C61" s="7">
         <v>302029</v>
       </c>
-      <c r="D61" s="11" t="s">
+      <c r="D61" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="E61" s="11"/>
-      <c r="F61" s="13">
+      <c r="E61" s="8"/>
+      <c r="F61" s="16">
         <v>22.99</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="9" t="s">
+    <row r="62" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B62" s="9" t="s">
+      <c r="B62" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C62" s="10">
+      <c r="C62" s="7">
         <v>272499</v>
       </c>
-      <c r="D62" s="11" t="s">
+      <c r="D62" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="E62" s="11"/>
-      <c r="F62" s="13">
+      <c r="E62" s="8"/>
+      <c r="F62" s="16">
         <v>23.49</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="9" t="s">
+    <row r="63" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B63" s="9" t="s">
+      <c r="B63" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C63" s="10">
+      <c r="C63" s="7">
         <v>292399</v>
       </c>
-      <c r="D63" s="11" t="s">
+      <c r="D63" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="E63" s="11"/>
-      <c r="F63" s="13">
+      <c r="E63" s="8"/>
+      <c r="F63" s="16">
         <v>10.99</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="86" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;LGIRO DA PRAÇA - SABADO E DOMINGO&amp;C&amp;P - &amp;N</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - SABADO E DOMINGO.xlsx
+++ b/giro_da_praça_ofertas - SABADO E DOMINGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F46680-B481-497F-A142-6BB7B65FF5BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B6CFA7-9B9E-464E-931C-6D1996E8D967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -687,6 +687,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F56"/>
   <sheetFormatPr defaultRowHeight="42.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1641,6 +1644,10 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;LGIRO DA PRAÇA - SABADO E DOMINGO&amp;C&amp;P - &amp;N</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - SABADO E DOMINGO.xlsx
+++ b/giro_da_praça_ofertas - SABADO E DOMINGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5208EA0C-D053-483F-98AE-B569D6EC8861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{362F42BB-E1A6-4D21-B28A-B30458DD8C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -182,7 +182,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -195,38 +195,27 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="16"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -270,34 +259,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -604,613 +587,614 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F35"/>
-  <sheetFormatPr defaultRowHeight="40.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" style="9" customWidth="1"/>
-    <col min="4" max="4" width="85.42578125" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="5">
         <v>341479</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8">
+      <c r="E2" s="6"/>
+      <c r="F2" s="7">
         <v>14.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="5">
         <v>102278</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8">
+      <c r="E3" s="6"/>
+      <c r="F3" s="7">
         <v>8.99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="5">
         <v>325127</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="8">
+      <c r="E4" s="6"/>
+      <c r="F4" s="7">
         <v>6.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="5">
         <v>257717</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="8">
+      <c r="E5" s="6"/>
+      <c r="F5" s="7">
         <v>7.69</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="5">
         <v>102282</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="8">
+      <c r="E6" s="6"/>
+      <c r="F6" s="7">
         <v>8.99</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="5">
         <v>341339</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8">
+      <c r="E7" s="6"/>
+      <c r="F7" s="7">
         <v>11.99</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="5">
         <v>342217</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8">
+      <c r="E8" s="6"/>
+      <c r="F8" s="7">
         <v>5.99</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="5">
         <v>303282</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="8">
+      <c r="E9" s="6"/>
+      <c r="F9" s="7">
         <v>5.99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="5">
         <v>286362</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="8">
+      <c r="E10" s="6"/>
+      <c r="F10" s="7">
         <v>9.89</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="2" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C11" s="5">
         <v>247785</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="8">
+      <c r="E11" s="6"/>
+      <c r="F11" s="7">
         <f>15*3.59</f>
         <v>53.849999999999994</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="2" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C12" s="5">
         <v>271001</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="8">
+      <c r="E12" s="6"/>
+      <c r="F12" s="7">
         <f>15*3.19</f>
         <v>47.85</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="2" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C13" s="5">
         <v>149113</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="8">
+      <c r="E13" s="6"/>
+      <c r="F13" s="7">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="2" t="s">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C14" s="5">
         <v>193636</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="8">
+      <c r="E14" s="6"/>
+      <c r="F14" s="7">
         <v>13.99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="2" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C15" s="5">
         <v>342201</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="7"/>
-      <c r="F15" s="8">
+      <c r="E15" s="6"/>
+      <c r="F15" s="7">
         <v>23.99</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="2" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C16" s="5">
         <v>158451</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="8">
+      <c r="E16" s="6"/>
+      <c r="F16" s="7">
         <v>29.99</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" s="2" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="5">
         <v>301843</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="8">
+      <c r="E17" s="6"/>
+      <c r="F17" s="7">
         <v>78.989999999999995</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="2" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C18" s="5">
         <v>134156</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="8">
+      <c r="E18" s="6"/>
+      <c r="F18" s="7">
         <v>52.99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" s="2" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C19" s="5">
         <v>102087</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="7"/>
-      <c r="F19" s="8">
+      <c r="E19" s="6"/>
+      <c r="F19" s="7">
         <v>48.99</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="2" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C20" s="5">
         <v>137381</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="8">
+      <c r="E20" s="6"/>
+      <c r="F20" s="7">
         <v>129.99</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="2" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C21" s="5">
         <v>102082</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="7"/>
-      <c r="F21" s="8">
+      <c r="E21" s="6"/>
+      <c r="F21" s="7">
         <v>72.989999999999995</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C23" s="5">
         <v>322739</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="7">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C24" s="5">
         <v>290589</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E24" s="7"/>
-      <c r="F24" s="8">
+      <c r="E24" s="6"/>
+      <c r="F24" s="7">
         <v>20.89</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="4" t="s">
         <v>38</v>
       </c>
       <c r="C25" s="5">
         <v>158733</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="7"/>
-      <c r="F25" s="8">
+      <c r="E25" s="6"/>
+      <c r="F25" s="7">
         <v>11.29</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C27" s="5">
         <v>111324</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E27" s="7"/>
-      <c r="F27" s="8">
+      <c r="E27" s="6"/>
+      <c r="F27" s="7">
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C28" s="5">
         <v>104602</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E28" s="7"/>
-      <c r="F28" s="8">
+      <c r="E28" s="6"/>
+      <c r="F28" s="7">
         <v>12.89</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C29" s="5">
         <v>108856</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E29" s="7"/>
-      <c r="F29" s="8">
+      <c r="E29" s="6"/>
+      <c r="F29" s="7">
         <v>23.19</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C30" s="5">
         <v>108788</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E30" s="7"/>
-      <c r="F30" s="8">
+      <c r="E30" s="6"/>
+      <c r="F30" s="7">
         <v>17.89</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C31" s="5">
         <v>105713</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E31" s="7"/>
-      <c r="F31" s="8">
+      <c r="E31" s="6"/>
+      <c r="F31" s="7">
         <v>23.19</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C32" s="5">
         <v>301962</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E32" s="7"/>
-      <c r="F32" s="8">
+      <c r="E32" s="6"/>
+      <c r="F32" s="7">
         <v>15.89</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C33" s="5">
         <v>168915</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E33" s="7"/>
-      <c r="F33" s="8">
+      <c r="E33" s="6"/>
+      <c r="F33" s="7">
         <v>6.19</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C34" s="5">
         <v>105765</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D34" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E34" s="7"/>
-      <c r="F34" s="8">
+      <c r="E34" s="6"/>
+      <c r="F34" s="7">
         <v>12.32</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C35" s="5">
         <v>119916</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D35" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E35" s="7"/>
-      <c r="F35" s="8">
+      <c r="E35" s="6"/>
+      <c r="F35" s="7">
         <v>14.79</v>
       </c>
     </row>
